--- a/static/data/exports/Retro_KL_AE_2016.xlsx
+++ b/static/data/exports/Retro_KL_AE_2016.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_KL_AE_2016.xlsx
+++ b/static/data/exports/Retro_KL_AE_2016.xlsx
@@ -45684,11 +45684,11 @@
     </row>
     <row r="734">
       <c r="A734" t="n">
-        <v>1705534</v>
+        <v>1705533</v>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>P K Yousef Panthalakkodath</t>
+          <t>Yussuf Kodoppilly</t>
         </is>
       </c>
       <c r="C734" t="inlineStr">
@@ -45721,7 +45721,7 @@
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>P K Yousef Panthalakkodath</t>
+          <t>Yussuf Kodoppilly</t>
         </is>
       </c>
       <c r="L734" t="inlineStr">
@@ -45746,11 +45746,11 @@
     </row>
     <row r="735">
       <c r="A735" t="n">
-        <v>1705533</v>
+        <v>1705534</v>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>Yussuf Kodoppilly</t>
+          <t>P K Yousef Panthalakkodath</t>
         </is>
       </c>
       <c r="C735" t="inlineStr">
@@ -45783,7 +45783,7 @@
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>Yussuf Kodoppilly</t>
+          <t>P K Yousef Panthalakkodath</t>
         </is>
       </c>
       <c r="L735" t="inlineStr">
@@ -64932,20 +64932,20 @@
     </row>
     <row r="1046">
       <c r="A1046" t="n">
-        <v>1707858</v>
+        <v>1707859</v>
       </c>
       <c r="B1046" t="inlineStr">
         <is>
-          <t>Kattanam Suresh</t>
+          <t>Ajeeshkumar</t>
         </is>
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D1046" t="n">
-        <v>19704</v>
+        <v>19702</v>
       </c>
       <c r="E1046" t="n">
         <v>213</v>
@@ -64969,12 +64969,12 @@
       </c>
       <c r="K1046" t="inlineStr">
         <is>
-          <t>Kattanam Suresh</t>
+          <t>Ajeeshkumar</t>
         </is>
       </c>
       <c r="L1046" t="inlineStr">
         <is>
-          <t>BSP</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="Q1046" t="b">
@@ -64994,20 +64994,20 @@
     </row>
     <row r="1047">
       <c r="A1047" t="n">
-        <v>1707859</v>
+        <v>1707858</v>
       </c>
       <c r="B1047" t="inlineStr">
         <is>
-          <t>Ajeeshkumar</t>
+          <t>Kattanam Suresh</t>
         </is>
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="D1047" t="n">
-        <v>19702</v>
+        <v>19704</v>
       </c>
       <c r="E1047" t="n">
         <v>213</v>
@@ -65031,12 +65031,12 @@
       </c>
       <c r="K1047" t="inlineStr">
         <is>
-          <t>Ajeeshkumar</t>
+          <t>Kattanam Suresh</t>
         </is>
       </c>
       <c r="L1047" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BSP</t>
         </is>
       </c>
       <c r="Q1047" t="b">
